--- a/Global/OMIS/OMIS_Headers.xlsx
+++ b/Global/OMIS/OMIS_Headers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\51000689\Documents\GitHub\clinical-data-collection\Global\OMIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E28DC18-51C6-4089-B69D-DA374EB118BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082B616D-A36D-4F71-9ACF-510B13160510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="960" windowWidth="48060" windowHeight="19350" activeTab="3" xr2:uid="{D94A1CE6-4507-4A65-B0C7-9031AC801546}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="55740" windowHeight="22290" activeTab="3" xr2:uid="{D94A1CE6-4507-4A65-B0C7-9031AC801546}"/>
   </bookViews>
   <sheets>
     <sheet name="Short" sheetId="1" r:id="rId1"/>
@@ -795,7 +795,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="779">
   <si>
     <t>PerformanceStatus</t>
   </si>
@@ -3630,6 +3630,15 @@
   </si>
   <si>
     <t>SystemicTherapyProtocolCycleNumber</t>
+  </si>
+  <si>
+    <t>Extract Date</t>
+  </si>
+  <si>
+    <t>ExtractDate</t>
+  </si>
+  <si>
+    <t>NOT500</t>
   </si>
 </sst>
 </file>
@@ -5316,9 +5325,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5356,7 +5365,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5462,7 +5471,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5604,7 +5613,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -12426,7 +12435,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334282CC-DFA0-48FD-AD80-F17EF0D3CFB1}">
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -14609,7 +14618,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>678</v>
       </c>
@@ -14626,7 +14635,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>684</v>
       </c>
@@ -14643,7 +14652,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>688</v>
       </c>
@@ -14660,7 +14669,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>693</v>
       </c>
@@ -14677,7 +14686,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>697</v>
       </c>
@@ -14694,7 +14703,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>701</v>
       </c>
@@ -14711,7 +14720,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>705</v>
       </c>
@@ -14728,7 +14737,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>709</v>
       </c>
@@ -14743,6 +14752,26 @@
       </c>
       <c r="F120" t="s">
         <v>710</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>778</v>
+      </c>
+      <c r="B121">
+        <v>120</v>
+      </c>
+      <c r="D121" t="s">
+        <v>194</v>
+      </c>
+      <c r="E121" t="s">
+        <v>776</v>
+      </c>
+      <c r="F121" t="s">
+        <v>777</v>
+      </c>
+      <c r="G121" t="s">
+        <v>769</v>
       </c>
     </row>
   </sheetData>

--- a/Global/OMIS/OMIS_Headers.xlsx
+++ b/Global/OMIS/OMIS_Headers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\51000689\Documents\GitHub\clinical-data-collection\Global\OMIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082B616D-A36D-4F71-9ACF-510B13160510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFA0FA3-9608-4B0C-BCC5-611A55AC4972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="55740" windowHeight="22290" activeTab="3" xr2:uid="{D94A1CE6-4507-4A65-B0C7-9031AC801546}"/>
   </bookViews>
@@ -14761,6 +14761,9 @@
       <c r="B121">
         <v>120</v>
       </c>
+      <c r="C121">
+        <v>63</v>
+      </c>
       <c r="D121" t="s">
         <v>194</v>
       </c>

--- a/Global/OMIS/OMIS_Headers.xlsx
+++ b/Global/OMIS/OMIS_Headers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\51000689\Documents\GitHub\clinical-data-collection\Global\OMIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFA0FA3-9608-4B0C-BCC5-611A55AC4972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C800B9-4296-4509-9E72-0F31B59A9771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="55740" windowHeight="22290" activeTab="3" xr2:uid="{D94A1CE6-4507-4A65-B0C7-9031AC801546}"/>
   </bookViews>
@@ -795,7 +795,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="778">
   <si>
     <t>PerformanceStatus</t>
   </si>
@@ -3630,9 +3630,6 @@
   </si>
   <si>
     <t>SystemicTherapyProtocolCycleNumber</t>
-  </si>
-  <si>
-    <t>Extract Date</t>
   </si>
   <si>
     <t>ExtractDate</t>
@@ -14756,7 +14753,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B121">
         <v>120</v>
@@ -14771,7 +14768,7 @@
         <v>776</v>
       </c>
       <c r="F121" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G121" t="s">
         <v>769</v>

--- a/Global/OMIS/OMIS_Headers.xlsx
+++ b/Global/OMIS/OMIS_Headers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\51000689\Documents\GitHub\clinical-data-collection\Global\OMIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C800B9-4296-4509-9E72-0F31B59A9771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB365B92-77D8-4B44-98D4-DB69D56C95D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="55740" windowHeight="22290" activeTab="3" xr2:uid="{D94A1CE6-4507-4A65-B0C7-9031AC801546}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{D94A1CE6-4507-4A65-B0C7-9031AC801546}"/>
   </bookViews>
   <sheets>
     <sheet name="Short" sheetId="1" r:id="rId1"/>
@@ -550,7 +550,7 @@
     <author>Matthew Wellings</author>
   </authors>
   <commentList>
-    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{9996B5AF-EED7-4D03-AD2C-B5AB78A4E472}">
+    <comment ref="E36" authorId="0" shapeId="0" xr:uid="{9996B5AF-EED7-4D03-AD2C-B5AB78A4E472}">
       <text>
         <r>
           <rPr>
@@ -574,7 +574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A60" authorId="0" shapeId="0" xr:uid="{C26E805E-2AEF-48C0-BCAC-EC218B6D3BFF}">
+    <comment ref="A61" authorId="0" shapeId="0" xr:uid="{C26E805E-2AEF-48C0-BCAC-EC218B6D3BFF}">
       <text>
         <r>
           <rPr>
@@ -598,7 +598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F72" authorId="0" shapeId="0" xr:uid="{78DB9895-029D-479B-91B8-1C69A797A4B6}">
+    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{78DB9895-029D-479B-91B8-1C69A797A4B6}">
       <text>
         <r>
           <rPr>
@@ -622,7 +622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{D9180E76-D9EF-471E-A3EE-CBF0F00311C0}">
+    <comment ref="A74" authorId="0" shapeId="0" xr:uid="{D9180E76-D9EF-471E-A3EE-CBF0F00311C0}">
       <text>
         <r>
           <rPr>
@@ -646,7 +646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A107" authorId="0" shapeId="0" xr:uid="{FA748BC4-EF01-4357-8B24-183937AE9080}">
+    <comment ref="A108" authorId="0" shapeId="0" xr:uid="{FA748BC4-EF01-4357-8B24-183937AE9080}">
       <text>
         <r>
           <rPr>
@@ -670,7 +670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A108" authorId="0" shapeId="0" xr:uid="{67E4061E-E070-403F-8D63-B800CE31640B}">
+    <comment ref="A109" authorId="0" shapeId="0" xr:uid="{67E4061E-E070-403F-8D63-B800CE31640B}">
       <text>
         <r>
           <rPr>
@@ -694,7 +694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A109" authorId="0" shapeId="0" xr:uid="{66754ED6-5294-4289-A520-03093E1CDE52}">
+    <comment ref="A110" authorId="0" shapeId="0" xr:uid="{66754ED6-5294-4289-A520-03093E1CDE52}">
       <text>
         <r>
           <rPr>
@@ -718,7 +718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A110" authorId="0" shapeId="0" xr:uid="{A23805B9-7BC9-4CD8-AC24-D64229370AB9}">
+    <comment ref="A111" authorId="0" shapeId="0" xr:uid="{A23805B9-7BC9-4CD8-AC24-D64229370AB9}">
       <text>
         <r>
           <rPr>
@@ -742,7 +742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A111" authorId="0" shapeId="0" xr:uid="{0FE99F28-CAD3-4B42-87EB-FAF3D8F4573F}">
+    <comment ref="A112" authorId="0" shapeId="0" xr:uid="{0FE99F28-CAD3-4B42-87EB-FAF3D8F4573F}">
       <text>
         <r>
           <rPr>
@@ -766,7 +766,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A112" authorId="0" shapeId="0" xr:uid="{C000DFAE-9C04-474A-BC18-629DA050A5D4}">
+    <comment ref="A113" authorId="0" shapeId="0" xr:uid="{C000DFAE-9C04-474A-BC18-629DA050A5D4}">
       <text>
         <r>
           <rPr>
@@ -795,7 +795,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="778">
   <si>
     <t>PerformanceStatus</t>
   </si>
@@ -12432,7 +12432,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334282CC-DFA0-48FD-AD80-F17EF0D3CFB1}">
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -12481,7 +12481,7 @@
         <v>193</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>207</v>
       </c>
       <c r="F2" t="s">
         <v>207</v>
@@ -12492,65 +12492,65 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>215</v>
+        <v>61</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>193</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>216</v>
+        <v>207</v>
+      </c>
+      <c r="G3" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" t="s">
-        <v>769</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>224</v>
+        <v>59</v>
       </c>
       <c r="G5" t="s">
         <v>769</v>
@@ -12558,179 +12558,179 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E6" t="s">
-        <v>233</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>230</v>
+        <v>224</v>
+      </c>
+      <c r="G6" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
         <v>194</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="F7" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
         <v>194</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" t="s">
-        <v>769</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
         <v>194</v>
       </c>
       <c r="E9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>240</v>
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
       </c>
       <c r="D10" t="s">
         <v>194</v>
       </c>
       <c r="E10" t="s">
-        <v>246</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
         <v>194</v>
       </c>
       <c r="E11" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F11" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
         <v>194</v>
       </c>
       <c r="E12" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F12" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>254</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" t="s">
-        <v>769</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
-        <v>260</v>
+        <v>53</v>
       </c>
       <c r="G14" t="s">
         <v>769</v>
@@ -12738,22 +12738,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G15" t="s">
         <v>769</v>
@@ -12761,22 +12761,25 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s">
-        <v>270</v>
+        <v>265</v>
+      </c>
+      <c r="G16" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -12784,16 +12787,19 @@
         <v>269</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>12</v>
       </c>
       <c r="D17" t="s">
         <v>194</v>
       </c>
       <c r="E17" t="s">
-        <v>279</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -12801,16 +12807,16 @@
         <v>269</v>
       </c>
       <c r="B18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
         <v>194</v>
       </c>
       <c r="E18" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F18" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -12818,59 +12824,53 @@
         <v>269</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
         <v>194</v>
       </c>
       <c r="E19" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F19" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="B20">
-        <v>19</v>
-      </c>
-      <c r="C20">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
         <v>194</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>287</v>
       </c>
       <c r="F20" t="s">
-        <v>289</v>
-      </c>
-      <c r="G20" t="s">
-        <v>769</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
         <v>194</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="G21" t="s">
         <v>769</v>
@@ -12878,22 +12878,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
         <v>194</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G22" t="s">
         <v>769</v>
@@ -12901,136 +12901,136 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B23">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="C23">
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E23" t="s">
-        <v>306</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>304</v>
+        <v>299</v>
+      </c>
+      <c r="G23" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B24">
-        <v>23</v>
-      </c>
-      <c r="C24">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
         <v>193</v>
       </c>
       <c r="E24" t="s">
+        <v>306</v>
+      </c>
+      <c r="F24" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>307</v>
+      </c>
+      <c r="B25">
+        <v>23</v>
+      </c>
+      <c r="C25">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
+        <v>193</v>
+      </c>
+      <c r="E25" t="s">
         <v>46</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F25" t="s">
         <v>308</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G25" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>312</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>24</v>
-      </c>
-      <c r="D25" t="s">
-        <v>194</v>
-      </c>
-      <c r="E25" t="s">
-        <v>316</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>317</v>
-      </c>
-      <c r="B26">
-        <v>25</v>
       </c>
       <c r="D26" t="s">
         <v>194</v>
       </c>
       <c r="E26" t="s">
-        <v>321</v>
-      </c>
-      <c r="F26" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
         <v>194</v>
       </c>
       <c r="E27" t="s">
-        <v>326</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
+      </c>
+      <c r="F27" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B28">
-        <v>27</v>
-      </c>
-      <c r="C28">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
         <v>194</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>326</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="G28" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
         <v>194</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" t="s">
-        <v>332</v>
+        <v>45</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="G29" t="s">
         <v>769</v>
@@ -13038,42 +13038,42 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B30">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="C30">
+        <v>18</v>
       </c>
       <c r="D30" t="s">
         <v>194</v>
       </c>
       <c r="E30" t="s">
-        <v>337</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s">
-        <v>335</v>
+        <v>332</v>
+      </c>
+      <c r="G30" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B31">
-        <v>30</v>
-      </c>
-      <c r="C31">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
         <v>194</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>337</v>
       </c>
       <c r="F31" t="s">
-        <v>340</v>
-      </c>
-      <c r="G31" t="s">
-        <v>767</v>
+        <v>335</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -13081,19 +13081,19 @@
         <v>339</v>
       </c>
       <c r="B32">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s">
         <v>194</v>
       </c>
       <c r="E32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F32" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G32" t="s">
         <v>767</v>
@@ -13101,151 +13101,151 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>339</v>
+      </c>
+      <c r="B33">
+        <v>31</v>
+      </c>
+      <c r="C33">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
+        <v>194</v>
+      </c>
+      <c r="E33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" t="s">
+        <v>344</v>
+      </c>
+      <c r="G33" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>347</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>32</v>
       </c>
-      <c r="C33">
+      <c r="C34">
         <v>21</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>195</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E34" t="s">
         <v>41</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>348</v>
-      </c>
-      <c r="G33" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>350</v>
-      </c>
-      <c r="B34">
-        <v>33</v>
-      </c>
-      <c r="C34">
-        <v>22</v>
-      </c>
-      <c r="D34" t="s">
-        <v>194</v>
-      </c>
-      <c r="E34" t="s">
-        <v>40</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="G34" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>350</v>
       </c>
       <c r="B35">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D35" t="s">
         <v>194</v>
       </c>
       <c r="E35" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" t="s">
-        <v>354</v>
+        <v>40</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G35" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B36">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F36" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B37">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F37" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B38">
+        <v>36</v>
+      </c>
+      <c r="C38">
+        <v>25</v>
+      </c>
+      <c r="D38" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38" t="s">
         <v>37</v>
       </c>
-      <c r="C38">
-        <v>26</v>
-      </c>
-      <c r="D38" t="s">
-        <v>193</v>
-      </c>
-      <c r="E38" t="s">
-        <v>36</v>
-      </c>
       <c r="F38" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B39">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C39">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F39" t="s">
-        <v>371</v>
-      </c>
-      <c r="G39" t="s">
-        <v>768</v>
+        <v>367</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -13253,107 +13253,113 @@
         <v>370</v>
       </c>
       <c r="B40">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D40" t="s">
         <v>194</v>
       </c>
       <c r="E40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F40" t="s">
-        <v>374</v>
+        <v>371</v>
+      </c>
+      <c r="G40" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B41">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="C41">
+        <v>28</v>
       </c>
       <c r="D41" t="s">
         <v>194</v>
       </c>
       <c r="E41" t="s">
-        <v>382</v>
+        <v>34</v>
       </c>
       <c r="F41" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B42">
-        <v>41</v>
-      </c>
-      <c r="C42">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>382</v>
       </c>
       <c r="F42" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B43">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="C43">
+        <v>29</v>
       </c>
       <c r="D43" t="s">
         <v>193</v>
       </c>
       <c r="E43" t="s">
-        <v>392</v>
+        <v>33</v>
       </c>
       <c r="F43" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B44">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E44" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F44" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B45">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E45" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F45" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -13361,1416 +13367,1433 @@
         <v>397</v>
       </c>
       <c r="B46">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
         <v>194</v>
       </c>
       <c r="E46" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F46" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B47">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E47" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F47" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>405</v>
+      </c>
+      <c r="B48">
+        <v>46</v>
+      </c>
+      <c r="D48" t="s">
+        <v>193</v>
+      </c>
+      <c r="E48" t="s">
+        <v>408</v>
+      </c>
+      <c r="F48" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>410</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>47</v>
       </c>
-      <c r="C48">
+      <c r="C49">
         <v>30</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>196</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E49" t="s">
         <v>32</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F49" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>414</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>48</v>
       </c>
-      <c r="C49">
+      <c r="C50">
         <v>31</v>
-      </c>
-      <c r="D49" t="s">
-        <v>194</v>
-      </c>
-      <c r="E49" t="s">
-        <v>31</v>
-      </c>
-      <c r="F49" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>419</v>
-      </c>
-      <c r="B50">
-        <v>49</v>
       </c>
       <c r="D50" t="s">
         <v>194</v>
       </c>
       <c r="E50" t="s">
-        <v>424</v>
+        <v>31</v>
       </c>
       <c r="F50" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B51">
-        <v>50</v>
-      </c>
-      <c r="C51">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D51" t="s">
         <v>194</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>424</v>
       </c>
       <c r="F51" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B52">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="C52">
+        <v>32</v>
       </c>
       <c r="D52" t="s">
         <v>194</v>
       </c>
       <c r="E52" t="s">
-        <v>432</v>
+        <v>30</v>
       </c>
       <c r="F52" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B53">
-        <v>52</v>
-      </c>
-      <c r="C53">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D53" t="s">
         <v>194</v>
       </c>
       <c r="E53" t="s">
-        <v>29</v>
+        <v>432</v>
       </c>
       <c r="F53" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B54">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="C54">
+        <v>33</v>
       </c>
       <c r="D54" t="s">
         <v>194</v>
       </c>
       <c r="E54" t="s">
-        <v>440</v>
+        <v>29</v>
       </c>
       <c r="F54" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B55">
-        <v>54</v>
-      </c>
-      <c r="C55">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D55" t="s">
         <v>194</v>
       </c>
       <c r="E55" t="s">
-        <v>28</v>
+        <v>440</v>
       </c>
       <c r="F55" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B56">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C56">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D56" t="s">
         <v>194</v>
       </c>
       <c r="E56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>446</v>
+      </c>
+      <c r="B57">
+        <v>55</v>
+      </c>
+      <c r="C57">
+        <v>35</v>
+      </c>
+      <c r="D57" t="s">
+        <v>194</v>
+      </c>
+      <c r="E57" t="s">
         <v>27</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F57" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>449</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>56</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D58" t="s">
         <v>193</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E58" t="s">
         <v>453</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F58" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>454</v>
       </c>
-      <c r="B58">
+      <c r="B59">
         <v>57</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D59" t="s">
         <v>194</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E59" t="s">
         <v>458</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F59" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>460</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>58</v>
       </c>
-      <c r="C59">
+      <c r="C60">
         <v>36</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D60" t="s">
         <v>196</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E60" t="s">
         <v>26</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F60" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>463</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>59</v>
       </c>
-      <c r="C60">
+      <c r="C61">
         <v>37</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D61" t="s">
         <v>193</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E61" t="s">
         <v>25</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F61" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>466</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>60</v>
       </c>
-      <c r="C61">
+      <c r="C62">
         <v>38</v>
-      </c>
-      <c r="D61" t="s">
-        <v>194</v>
-      </c>
-      <c r="E61" t="s">
-        <v>24</v>
-      </c>
-      <c r="F61" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>471</v>
-      </c>
-      <c r="B62">
-        <v>61</v>
-      </c>
-      <c r="C62">
-        <v>39</v>
       </c>
       <c r="D62" t="s">
         <v>194</v>
       </c>
       <c r="E62" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>471</v>
+      </c>
+      <c r="B63">
+        <v>61</v>
+      </c>
+      <c r="C63">
+        <v>39</v>
+      </c>
+      <c r="D63" t="s">
+        <v>194</v>
+      </c>
+      <c r="E63" t="s">
         <v>474</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F63" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>475</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <v>62</v>
-      </c>
-      <c r="D63" t="s">
-        <v>193</v>
-      </c>
-      <c r="E63" t="s">
-        <v>479</v>
-      </c>
-      <c r="F63" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>481</v>
-      </c>
-      <c r="B64">
-        <v>63</v>
-      </c>
-      <c r="C64">
-        <v>40</v>
       </c>
       <c r="D64" t="s">
         <v>193</v>
       </c>
       <c r="E64" t="s">
-        <v>22</v>
+        <v>479</v>
       </c>
       <c r="F64" t="s">
-        <v>482</v>
-      </c>
-      <c r="G64" t="s">
-        <v>769</v>
+        <v>476</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B65">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="C65">
+        <v>40</v>
       </c>
       <c r="D65" t="s">
         <v>193</v>
       </c>
       <c r="E65" t="s">
-        <v>488</v>
+        <v>22</v>
       </c>
       <c r="F65" t="s">
-        <v>486</v>
+        <v>482</v>
+      </c>
+      <c r="G65" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B66">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D66" t="s">
         <v>193</v>
       </c>
       <c r="E66" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F66" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B67">
-        <v>66</v>
-      </c>
-      <c r="C67">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="D67" t="s">
         <v>193</v>
       </c>
       <c r="E67" t="s">
-        <v>21</v>
+        <v>492</v>
       </c>
       <c r="F67" t="s">
-        <v>494</v>
-      </c>
-      <c r="G67" t="s">
-        <v>769</v>
+        <v>490</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B68">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="C68">
+        <v>41</v>
       </c>
       <c r="D68" t="s">
         <v>193</v>
       </c>
       <c r="E68" t="s">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="F68" t="s">
-        <v>497</v>
+        <v>494</v>
+      </c>
+      <c r="G68" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B69">
-        <v>68</v>
-      </c>
-      <c r="C69">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D69" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E69" t="s">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="F69" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B70">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C70">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D70" t="s">
         <v>195</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F70" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B71">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C71">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D71" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E71" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F71" t="s">
-        <v>508</v>
-      </c>
-      <c r="G71" t="s">
-        <v>768</v>
+        <v>505</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B72">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C72">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D72" t="s">
         <v>193</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F72" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="G72" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B73">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C73">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D73" t="s">
         <v>193</v>
       </c>
       <c r="E73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F73" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="G73" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B74">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C74">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D74" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F74" t="s">
-        <v>522</v>
+        <v>518</v>
+      </c>
+      <c r="G74" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B75">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C75">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D75" t="s">
         <v>194</v>
       </c>
       <c r="E75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F75" t="s">
-        <v>135</v>
+        <v>522</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B76">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C76">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D76" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E76" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F76" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B77">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C77">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E77" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F77" t="s">
-        <v>532</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B78">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C78">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D78" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E78" t="s">
-        <v>774</v>
+        <v>12</v>
       </c>
       <c r="F78" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B79">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C79">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D79" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E79" t="s">
-        <v>10</v>
+        <v>774</v>
       </c>
       <c r="F79" t="s">
-        <v>139</v>
+        <v>536</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B80">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C80">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D80" t="s">
         <v>197</v>
       </c>
       <c r="E80" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>543</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B81">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C81">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D81" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E81" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F81" t="s">
-        <v>141</v>
+        <v>543</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B82">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="C82">
+        <v>54</v>
       </c>
       <c r="D82" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E82" t="s">
-        <v>775</v>
+        <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>554</v>
-      </c>
-      <c r="G82" t="s">
-        <v>768</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B83">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D83" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E83" t="s">
-        <v>744</v>
+        <v>775</v>
       </c>
       <c r="F83" t="s">
-        <v>558</v>
+        <v>554</v>
+      </c>
+      <c r="G83" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B84">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D84" t="s">
         <v>195</v>
       </c>
       <c r="E84" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F84" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B85">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D85" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E85" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F85" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B86">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D86" t="s">
         <v>193</v>
       </c>
       <c r="E86" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F86" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B87">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D87" t="s">
         <v>193</v>
       </c>
       <c r="E87" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F87" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B88">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D88" t="s">
         <v>193</v>
       </c>
       <c r="E88" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F88" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B89">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D89" t="s">
         <v>193</v>
       </c>
       <c r="E89" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F89" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B90">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D90" t="s">
         <v>193</v>
       </c>
       <c r="E90" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F90" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B91">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D91" t="s">
         <v>193</v>
       </c>
       <c r="E91" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F91" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B92">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D92" t="s">
         <v>193</v>
       </c>
       <c r="E92" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F92" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B93">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D93" t="s">
         <v>193</v>
       </c>
       <c r="E93" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F93" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B94">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D94" t="s">
         <v>193</v>
       </c>
       <c r="E94" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F94" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="B95">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D95" t="s">
         <v>193</v>
       </c>
       <c r="E95" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F95" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B96">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D96" t="s">
         <v>193</v>
       </c>
       <c r="E96" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="F96" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B97">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D97" t="s">
         <v>193</v>
       </c>
       <c r="E97" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F97" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B98">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D98" t="s">
         <v>193</v>
       </c>
       <c r="E98" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F98" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B99">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D99" t="s">
         <v>193</v>
       </c>
       <c r="E99" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F99" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B100">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D100" t="s">
         <v>193</v>
       </c>
       <c r="E100" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F100" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B101">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D101" t="s">
         <v>193</v>
       </c>
       <c r="E101" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F101" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B102">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D102" t="s">
         <v>193</v>
       </c>
       <c r="E102" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F102" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B103">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D103" t="s">
         <v>193</v>
       </c>
       <c r="E103" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F103" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B104">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D104" t="s">
         <v>193</v>
       </c>
       <c r="E104" t="s">
+        <v>764</v>
+      </c>
+      <c r="F104" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>646</v>
+      </c>
+      <c r="B105">
+        <v>103</v>
+      </c>
+      <c r="D105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E105" t="s">
         <v>765</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F105" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+    <row r="106" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>334</v>
       </c>
-      <c r="B105">
+      <c r="B106">
         <v>104</v>
       </c>
-      <c r="C105">
+      <c r="C106">
         <v>55</v>
-      </c>
-      <c r="D105" t="s">
-        <v>195</v>
-      </c>
-      <c r="E105" t="s">
-        <v>7</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>653</v>
-      </c>
-      <c r="B106">
-        <v>105</v>
-      </c>
-      <c r="C106">
-        <v>56</v>
       </c>
       <c r="D106" t="s">
         <v>195</v>
       </c>
       <c r="E106" t="s">
-        <v>6</v>
-      </c>
-      <c r="F106" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B107">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C107">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D107" t="s">
         <v>195</v>
       </c>
       <c r="E107" t="s">
+        <v>6</v>
+      </c>
+      <c r="F107" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>656</v>
+      </c>
+      <c r="B108">
+        <v>106</v>
+      </c>
+      <c r="C108">
+        <v>57</v>
+      </c>
+      <c r="D108" t="s">
+        <v>195</v>
+      </c>
+      <c r="E108" t="s">
         <v>5</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="F108" s="1" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+    <row r="109" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>659</v>
       </c>
-      <c r="B108">
+      <c r="B109">
         <v>107</v>
       </c>
-      <c r="C108">
+      <c r="C109">
         <v>58</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D109" t="s">
         <v>194</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E109" t="s">
         <v>4</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="F109" s="1" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>663</v>
       </c>
-      <c r="B109">
+      <c r="B110">
         <v>108</v>
       </c>
-      <c r="C109">
+      <c r="C110">
         <v>59</v>
-      </c>
-      <c r="D109" t="s">
-        <v>195</v>
-      </c>
-      <c r="E109" t="s">
-        <v>3</v>
-      </c>
-      <c r="F109" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>666</v>
-      </c>
-      <c r="B110">
-        <v>109</v>
-      </c>
-      <c r="C110">
-        <v>60</v>
       </c>
       <c r="D110" t="s">
         <v>195</v>
       </c>
       <c r="E110" t="s">
-        <v>669</v>
+        <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B111">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C111">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D111" t="s">
         <v>195</v>
       </c>
       <c r="E111" t="s">
+        <v>669</v>
+      </c>
+      <c r="F111" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>670</v>
+      </c>
+      <c r="B112">
+        <v>110</v>
+      </c>
+      <c r="C112">
+        <v>61</v>
+      </c>
+      <c r="D112" t="s">
+        <v>195</v>
+      </c>
+      <c r="E112" t="s">
         <v>1</v>
       </c>
-      <c r="F111" t="s">
+      <c r="F112" t="s">
         <v>671</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>673</v>
-      </c>
-      <c r="B112">
-        <v>111</v>
-      </c>
-      <c r="C112">
-        <v>62</v>
-      </c>
-      <c r="D112" t="s">
-        <v>193</v>
-      </c>
-      <c r="E112" t="s">
-        <v>0</v>
-      </c>
-      <c r="F112" t="s">
-        <v>674</v>
-      </c>
-      <c r="G112" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="B113">
-        <v>112</v>
+        <v>111</v>
+      </c>
+      <c r="C113">
+        <v>62</v>
       </c>
       <c r="D113" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E113" t="s">
-        <v>683</v>
+        <v>0</v>
       </c>
       <c r="F113" t="s">
-        <v>679</v>
+        <v>674</v>
+      </c>
+      <c r="G113" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="B114">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D114" t="s">
         <v>194</v>
       </c>
       <c r="E114" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="F114" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B115">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D115" t="s">
         <v>194</v>
       </c>
       <c r="E115" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="F115" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="B116">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D116" t="s">
         <v>194</v>
       </c>
       <c r="E116" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F116" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B117">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D117" t="s">
         <v>194</v>
       </c>
       <c r="E117" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="F117" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B118">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D118" t="s">
         <v>194</v>
       </c>
       <c r="E118" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="F118" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B119">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D119" t="s">
         <v>194</v>
       </c>
       <c r="E119" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="F119" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B120">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D120" t="s">
         <v>194</v>
       </c>
       <c r="E120" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="F120" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>777</v>
+        <v>709</v>
       </c>
       <c r="B121">
-        <v>120</v>
-      </c>
-      <c r="C121">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="D121" t="s">
         <v>194</v>
       </c>
       <c r="E121" t="s">
+        <v>712</v>
+      </c>
+      <c r="F121" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>777</v>
+      </c>
+      <c r="B122">
+        <v>120</v>
+      </c>
+      <c r="C122">
+        <v>63</v>
+      </c>
+      <c r="D122" t="s">
+        <v>194</v>
+      </c>
+      <c r="E122" t="s">
         <v>776</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F122" t="s">
         <v>776</v>
       </c>
-      <c r="G121" t="s">
+      <c r="G122" t="s">
         <v>769</v>
       </c>
     </row>

--- a/Global/OMIS/OMIS_Headers.xlsx
+++ b/Global/OMIS/OMIS_Headers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\51000689\Documents\GitHub\clinical-data-collection\Global\OMIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB365B92-77D8-4B44-98D4-DB69D56C95D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81B6614-DD97-43C9-8C27-73651E74B04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{D94A1CE6-4507-4A65-B0C7-9031AC801546}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" activeTab="3" xr2:uid="{D94A1CE6-4507-4A65-B0C7-9031AC801546}"/>
   </bookViews>
   <sheets>
     <sheet name="Short" sheetId="1" r:id="rId1"/>
@@ -550,7 +550,7 @@
     <author>Matthew Wellings</author>
   </authors>
   <commentList>
-    <comment ref="E36" authorId="0" shapeId="0" xr:uid="{9996B5AF-EED7-4D03-AD2C-B5AB78A4E472}">
+    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{9996B5AF-EED7-4D03-AD2C-B5AB78A4E472}">
       <text>
         <r>
           <rPr>
@@ -574,7 +574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A61" authorId="0" shapeId="0" xr:uid="{C26E805E-2AEF-48C0-BCAC-EC218B6D3BFF}">
+    <comment ref="A60" authorId="0" shapeId="0" xr:uid="{C26E805E-2AEF-48C0-BCAC-EC218B6D3BFF}">
       <text>
         <r>
           <rPr>
@@ -598,7 +598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{78DB9895-029D-479B-91B8-1C69A797A4B6}">
+    <comment ref="F72" authorId="0" shapeId="0" xr:uid="{78DB9895-029D-479B-91B8-1C69A797A4B6}">
       <text>
         <r>
           <rPr>
@@ -622,7 +622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A74" authorId="0" shapeId="0" xr:uid="{D9180E76-D9EF-471E-A3EE-CBF0F00311C0}">
+    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{D9180E76-D9EF-471E-A3EE-CBF0F00311C0}">
       <text>
         <r>
           <rPr>
@@ -646,7 +646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A108" authorId="0" shapeId="0" xr:uid="{FA748BC4-EF01-4357-8B24-183937AE9080}">
+    <comment ref="A107" authorId="0" shapeId="0" xr:uid="{FA748BC4-EF01-4357-8B24-183937AE9080}">
       <text>
         <r>
           <rPr>
@@ -670,7 +670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A109" authorId="0" shapeId="0" xr:uid="{67E4061E-E070-403F-8D63-B800CE31640B}">
+    <comment ref="A108" authorId="0" shapeId="0" xr:uid="{67E4061E-E070-403F-8D63-B800CE31640B}">
       <text>
         <r>
           <rPr>
@@ -694,7 +694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A110" authorId="0" shapeId="0" xr:uid="{66754ED6-5294-4289-A520-03093E1CDE52}">
+    <comment ref="A109" authorId="0" shapeId="0" xr:uid="{66754ED6-5294-4289-A520-03093E1CDE52}">
       <text>
         <r>
           <rPr>
@@ -718,7 +718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A111" authorId="0" shapeId="0" xr:uid="{A23805B9-7BC9-4CD8-AC24-D64229370AB9}">
+    <comment ref="A110" authorId="0" shapeId="0" xr:uid="{A23805B9-7BC9-4CD8-AC24-D64229370AB9}">
       <text>
         <r>
           <rPr>
@@ -742,7 +742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A112" authorId="0" shapeId="0" xr:uid="{0FE99F28-CAD3-4B42-87EB-FAF3D8F4573F}">
+    <comment ref="A111" authorId="0" shapeId="0" xr:uid="{0FE99F28-CAD3-4B42-87EB-FAF3D8F4573F}">
       <text>
         <r>
           <rPr>
@@ -766,7 +766,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A113" authorId="0" shapeId="0" xr:uid="{C000DFAE-9C04-474A-BC18-629DA050A5D4}">
+    <comment ref="A112" authorId="0" shapeId="0" xr:uid="{C000DFAE-9C04-474A-BC18-629DA050A5D4}">
       <text>
         <r>
           <rPr>
@@ -795,7 +795,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="778">
   <si>
     <t>PerformanceStatus</t>
   </si>
@@ -12432,7 +12432,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334282CC-DFA0-48FD-AD80-F17EF0D3CFB1}">
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -12481,7 +12481,7 @@
         <v>193</v>
       </c>
       <c r="E2" t="s">
-        <v>207</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
         <v>207</v>
@@ -12492,65 +12492,65 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>215</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>193</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G3" t="s">
-        <v>767</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>216</v>
+        <v>59</v>
+      </c>
+      <c r="G4" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>224</v>
       </c>
       <c r="G5" t="s">
         <v>769</v>
@@ -12558,179 +12558,179 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>233</v>
       </c>
       <c r="F6" t="s">
-        <v>224</v>
-      </c>
-      <c r="G6" t="s">
-        <v>769</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
         <v>194</v>
       </c>
       <c r="E7" t="s">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
         <v>194</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>235</v>
+        <v>55</v>
+      </c>
+      <c r="G8" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
         <v>194</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" t="s">
-        <v>769</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B10">
-        <v>8</v>
-      </c>
-      <c r="C10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
         <v>194</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>246</v>
       </c>
       <c r="F10" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
         <v>194</v>
       </c>
       <c r="E11" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
         <v>194</v>
       </c>
       <c r="E12" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E13" t="s">
-        <v>254</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
-        <v>252</v>
+        <v>53</v>
+      </c>
+      <c r="G13" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>260</v>
       </c>
       <c r="G14" t="s">
         <v>769</v>
@@ -12738,22 +12738,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F15" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G15" t="s">
         <v>769</v>
@@ -12761,25 +12761,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F16" t="s">
-        <v>265</v>
-      </c>
-      <c r="G16" t="s">
-        <v>769</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -12787,19 +12784,16 @@
         <v>269</v>
       </c>
       <c r="B17">
-        <v>15</v>
-      </c>
-      <c r="C17">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
         <v>194</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>279</v>
       </c>
       <c r="F17" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -12807,16 +12801,16 @@
         <v>269</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
         <v>194</v>
       </c>
       <c r="E18" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F18" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -12824,53 +12818,59 @@
         <v>269</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
         <v>194</v>
       </c>
       <c r="E19" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F19" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="B20">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="C20">
+        <v>13</v>
       </c>
       <c r="D20" t="s">
         <v>194</v>
       </c>
       <c r="E20" t="s">
-        <v>287</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s">
-        <v>284</v>
+        <v>289</v>
+      </c>
+      <c r="G20" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
         <v>194</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G21" t="s">
         <v>769</v>
@@ -12878,22 +12878,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
         <v>194</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="G22" t="s">
         <v>769</v>
@@ -12901,136 +12901,136 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B23">
-        <v>21</v>
-      </c>
-      <c r="C23">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>306</v>
       </c>
       <c r="F23" t="s">
-        <v>299</v>
-      </c>
-      <c r="G23" t="s">
-        <v>769</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B24">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>16</v>
       </c>
       <c r="D24" t="s">
         <v>193</v>
       </c>
       <c r="E24" t="s">
-        <v>306</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+      <c r="G24" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B25">
-        <v>23</v>
-      </c>
-      <c r="C25">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E25" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" t="s">
-        <v>308</v>
-      </c>
-      <c r="G25" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
         <v>194</v>
       </c>
       <c r="E26" t="s">
-        <v>316</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+      <c r="F26" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
         <v>194</v>
       </c>
       <c r="E27" t="s">
-        <v>321</v>
-      </c>
-      <c r="F27" t="s">
-        <v>318</v>
+        <v>326</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B28">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="C28">
+        <v>17</v>
       </c>
       <c r="D28" t="s">
         <v>194</v>
       </c>
       <c r="E28" t="s">
-        <v>326</v>
+        <v>45</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+      <c r="G28" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B29">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C29">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
         <v>194</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>328</v>
+        <v>44</v>
+      </c>
+      <c r="F29" t="s">
+        <v>332</v>
       </c>
       <c r="G29" t="s">
         <v>769</v>
@@ -13038,42 +13038,42 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B30">
-        <v>28</v>
-      </c>
-      <c r="C30">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
         <v>194</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
+        <v>337</v>
       </c>
       <c r="F30" t="s">
-        <v>332</v>
-      </c>
-      <c r="G30" t="s">
-        <v>769</v>
+        <v>335</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B31">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>19</v>
       </c>
       <c r="D31" t="s">
         <v>194</v>
       </c>
       <c r="E31" t="s">
-        <v>337</v>
+        <v>43</v>
       </c>
       <c r="F31" t="s">
-        <v>335</v>
+        <v>340</v>
+      </c>
+      <c r="G31" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -13081,19 +13081,19 @@
         <v>339</v>
       </c>
       <c r="B32">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
         <v>194</v>
       </c>
       <c r="E32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F32" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G32" t="s">
         <v>767</v>
@@ -13101,151 +13101,151 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B33">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33" t="s">
+        <v>195</v>
+      </c>
+      <c r="E33" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33" t="s">
+        <v>348</v>
+      </c>
+      <c r="G33" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>350</v>
+      </c>
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>22</v>
+      </c>
+      <c r="D34" t="s">
         <v>194</v>
       </c>
-      <c r="E33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" t="s">
-        <v>344</v>
-      </c>
-      <c r="G33" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>347</v>
-      </c>
-      <c r="B34">
-        <v>32</v>
-      </c>
-      <c r="C34">
-        <v>21</v>
-      </c>
-      <c r="D34" t="s">
-        <v>195</v>
-      </c>
       <c r="E34" t="s">
-        <v>41</v>
-      </c>
-      <c r="F34" t="s">
-        <v>348</v>
+        <v>40</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="G34" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>350</v>
       </c>
       <c r="B35">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
         <v>194</v>
       </c>
       <c r="E35" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="G35" t="s">
-        <v>769</v>
+        <v>39</v>
+      </c>
+      <c r="F35" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B36">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F36" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B37">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F37" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B38">
+        <v>37</v>
+      </c>
+      <c r="C38">
+        <v>26</v>
+      </c>
+      <c r="D38" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" t="s">
         <v>36</v>
       </c>
-      <c r="C38">
-        <v>25</v>
-      </c>
-      <c r="D38" t="s">
-        <v>194</v>
-      </c>
-      <c r="E38" t="s">
-        <v>37</v>
-      </c>
       <c r="F38" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B39">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C39">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F39" t="s">
-        <v>367</v>
+        <v>371</v>
+      </c>
+      <c r="G39" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -13253,113 +13253,107 @@
         <v>370</v>
       </c>
       <c r="B40">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C40">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
         <v>194</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F40" t="s">
-        <v>371</v>
-      </c>
-      <c r="G40" t="s">
-        <v>768</v>
+        <v>374</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B41">
-        <v>39</v>
-      </c>
-      <c r="C41">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
         <v>194</v>
       </c>
       <c r="E41" t="s">
-        <v>34</v>
+        <v>382</v>
       </c>
       <c r="F41" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B42">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="C42">
+        <v>29</v>
       </c>
       <c r="D42" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E42" t="s">
-        <v>382</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B43">
-        <v>41</v>
-      </c>
-      <c r="C43">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D43" t="s">
         <v>193</v>
       </c>
       <c r="E43" t="s">
-        <v>33</v>
+        <v>392</v>
       </c>
       <c r="F43" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B44">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E44" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F44" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B45">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E45" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F45" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -13367,1433 +13361,1416 @@
         <v>397</v>
       </c>
       <c r="B46">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D46" t="s">
         <v>194</v>
       </c>
       <c r="E46" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F46" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B47">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E47" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F47" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B48">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="C48">
+        <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E48" t="s">
-        <v>408</v>
+        <v>32</v>
       </c>
       <c r="F48" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B49">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C49">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F49" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B50">
-        <v>48</v>
-      </c>
-      <c r="C50">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D50" t="s">
         <v>194</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>424</v>
       </c>
       <c r="F50" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B51">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="C51">
+        <v>32</v>
       </c>
       <c r="D51" t="s">
         <v>194</v>
       </c>
       <c r="E51" t="s">
-        <v>424</v>
+        <v>30</v>
       </c>
       <c r="F51" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B52">
-        <v>50</v>
-      </c>
-      <c r="C52">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D52" t="s">
         <v>194</v>
       </c>
       <c r="E52" t="s">
-        <v>30</v>
+        <v>432</v>
       </c>
       <c r="F52" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B53">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="C53">
+        <v>33</v>
       </c>
       <c r="D53" t="s">
         <v>194</v>
       </c>
       <c r="E53" t="s">
-        <v>432</v>
+        <v>29</v>
       </c>
       <c r="F53" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B54">
-        <v>52</v>
-      </c>
-      <c r="C54">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D54" t="s">
         <v>194</v>
       </c>
       <c r="E54" t="s">
-        <v>29</v>
+        <v>440</v>
       </c>
       <c r="F54" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B55">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="C55">
+        <v>34</v>
       </c>
       <c r="D55" t="s">
         <v>194</v>
       </c>
       <c r="E55" t="s">
-        <v>440</v>
+        <v>28</v>
       </c>
       <c r="F55" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B56">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C56">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D56" t="s">
         <v>194</v>
       </c>
       <c r="E56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F56" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B57">
-        <v>55</v>
-      </c>
-      <c r="C57">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D57" t="s">
+        <v>193</v>
+      </c>
+      <c r="E57" t="s">
+        <v>453</v>
+      </c>
+      <c r="F57" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>454</v>
+      </c>
+      <c r="B58">
+        <v>57</v>
+      </c>
+      <c r="D58" t="s">
         <v>194</v>
       </c>
-      <c r="E57" t="s">
-        <v>27</v>
-      </c>
-      <c r="F57" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>449</v>
-      </c>
-      <c r="B58">
-        <v>56</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
+        <v>458</v>
+      </c>
+      <c r="F58" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>460</v>
+      </c>
+      <c r="B59">
+        <v>58</v>
+      </c>
+      <c r="C59">
+        <v>36</v>
+      </c>
+      <c r="D59" t="s">
+        <v>196</v>
+      </c>
+      <c r="E59" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>463</v>
+      </c>
+      <c r="B60">
+        <v>59</v>
+      </c>
+      <c r="C60">
+        <v>37</v>
+      </c>
+      <c r="D60" t="s">
         <v>193</v>
       </c>
-      <c r="E58" t="s">
-        <v>453</v>
-      </c>
-      <c r="F58" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>454</v>
-      </c>
-      <c r="B59">
-        <v>57</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="E60" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>466</v>
+      </c>
+      <c r="B61">
+        <v>60</v>
+      </c>
+      <c r="C61">
+        <v>38</v>
+      </c>
+      <c r="D61" t="s">
         <v>194</v>
       </c>
-      <c r="E59" t="s">
-        <v>458</v>
-      </c>
-      <c r="F59" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>460</v>
-      </c>
-      <c r="B60">
-        <v>58</v>
-      </c>
-      <c r="C60">
-        <v>36</v>
-      </c>
-      <c r="D60" t="s">
-        <v>196</v>
-      </c>
-      <c r="E60" t="s">
-        <v>26</v>
-      </c>
-      <c r="F60" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>463</v>
-      </c>
-      <c r="B61">
-        <v>59</v>
-      </c>
-      <c r="C61">
-        <v>37</v>
-      </c>
-      <c r="D61" t="s">
-        <v>193</v>
-      </c>
       <c r="E61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F61" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B62">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C62">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D62" t="s">
         <v>194</v>
       </c>
       <c r="E62" t="s">
-        <v>24</v>
+        <v>474</v>
       </c>
       <c r="F62" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B63">
-        <v>61</v>
-      </c>
-      <c r="C63">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D63" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E63" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="F63" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B64">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="C64">
+        <v>40</v>
       </c>
       <c r="D64" t="s">
         <v>193</v>
       </c>
       <c r="E64" t="s">
-        <v>479</v>
+        <v>22</v>
       </c>
       <c r="F64" t="s">
-        <v>476</v>
+        <v>482</v>
+      </c>
+      <c r="G64" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B65">
-        <v>63</v>
-      </c>
-      <c r="C65">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D65" t="s">
         <v>193</v>
       </c>
       <c r="E65" t="s">
-        <v>22</v>
+        <v>488</v>
       </c>
       <c r="F65" t="s">
-        <v>482</v>
-      </c>
-      <c r="G65" t="s">
-        <v>769</v>
+        <v>486</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B66">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D66" t="s">
         <v>193</v>
       </c>
       <c r="E66" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F66" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B67">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="C67">
+        <v>41</v>
       </c>
       <c r="D67" t="s">
         <v>193</v>
       </c>
       <c r="E67" t="s">
-        <v>492</v>
+        <v>21</v>
       </c>
       <c r="F67" t="s">
-        <v>490</v>
+        <v>494</v>
+      </c>
+      <c r="G67" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B68">
-        <v>66</v>
-      </c>
-      <c r="C68">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D68" t="s">
         <v>193</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="F68" t="s">
-        <v>494</v>
-      </c>
-      <c r="G68" t="s">
-        <v>769</v>
+        <v>497</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B69">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="C69">
+        <v>42</v>
       </c>
       <c r="D69" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E69" t="s">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="F69" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B70">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C70">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D70" t="s">
         <v>195</v>
       </c>
       <c r="E70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F70" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B71">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C71">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F71" t="s">
-        <v>505</v>
+        <v>508</v>
+      </c>
+      <c r="G71" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B72">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C72">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D72" t="s">
         <v>193</v>
       </c>
       <c r="E72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F72" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="G72" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B73">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D73" t="s">
         <v>193</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F73" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="G73" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B74">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C74">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D74" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F74" t="s">
-        <v>518</v>
-      </c>
-      <c r="G74" t="s">
-        <v>768</v>
+        <v>522</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B75">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C75">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D75" t="s">
         <v>194</v>
       </c>
       <c r="E75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F75" t="s">
-        <v>522</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B76">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C76">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D76" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F76" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B77">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C77">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D77" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>136</v>
+        <v>532</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B78">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C78">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D78" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E78" t="s">
-        <v>12</v>
+        <v>774</v>
       </c>
       <c r="F78" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B79">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C79">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D79" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E79" t="s">
-        <v>774</v>
+        <v>10</v>
       </c>
       <c r="F79" t="s">
-        <v>536</v>
+        <v>139</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B80">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C80">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D80" t="s">
         <v>197</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F80" t="s">
-        <v>139</v>
+        <v>543</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B81">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C81">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D81" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>543</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B82">
-        <v>80</v>
-      </c>
-      <c r="C82">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="D82" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E82" t="s">
-        <v>8</v>
+        <v>775</v>
       </c>
       <c r="F82" t="s">
-        <v>141</v>
+        <v>554</v>
+      </c>
+      <c r="G82" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B83">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D83" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E83" t="s">
-        <v>775</v>
+        <v>744</v>
       </c>
       <c r="F83" t="s">
-        <v>554</v>
-      </c>
-      <c r="G83" t="s">
-        <v>768</v>
+        <v>558</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B84">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D84" t="s">
         <v>195</v>
       </c>
       <c r="E84" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F84" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B85">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D85" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E85" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F85" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B86">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D86" t="s">
         <v>193</v>
       </c>
       <c r="E86" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F86" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B87">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D87" t="s">
         <v>193</v>
       </c>
       <c r="E87" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F87" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B88">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D88" t="s">
         <v>193</v>
       </c>
       <c r="E88" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F88" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B89">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D89" t="s">
         <v>193</v>
       </c>
       <c r="E89" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F89" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B90">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D90" t="s">
         <v>193</v>
       </c>
       <c r="E90" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F90" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B91">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D91" t="s">
         <v>193</v>
       </c>
       <c r="E91" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F91" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B92">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s">
         <v>193</v>
       </c>
       <c r="E92" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F92" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B93">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D93" t="s">
         <v>193</v>
       </c>
       <c r="E93" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F93" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B94">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D94" t="s">
         <v>193</v>
       </c>
       <c r="E94" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F94" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B95">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D95" t="s">
         <v>193</v>
       </c>
       <c r="E95" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F95" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B96">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D96" t="s">
         <v>193</v>
       </c>
       <c r="E96" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F96" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B97">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D97" t="s">
         <v>193</v>
       </c>
       <c r="E97" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F97" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B98">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D98" t="s">
         <v>193</v>
       </c>
       <c r="E98" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F98" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B99">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D99" t="s">
         <v>193</v>
       </c>
       <c r="E99" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F99" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B100">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D100" t="s">
         <v>193</v>
       </c>
       <c r="E100" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F100" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B101">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D101" t="s">
         <v>193</v>
       </c>
       <c r="E101" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F101" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B102">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D102" t="s">
         <v>193</v>
       </c>
       <c r="E102" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F102" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B103">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D103" t="s">
         <v>193</v>
       </c>
       <c r="E103" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F103" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B104">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D104" t="s">
         <v>193</v>
       </c>
       <c r="E104" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F104" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>646</v>
+        <v>334</v>
       </c>
       <c r="B105">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="C105">
+        <v>55</v>
       </c>
       <c r="D105" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E105" t="s">
-        <v>765</v>
-      </c>
-      <c r="F105" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>334</v>
+        <v>653</v>
       </c>
       <c r="B106">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C106">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D106" t="s">
         <v>195</v>
       </c>
       <c r="E106" t="s">
-        <v>7</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="F106" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B107">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C107">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D107" t="s">
         <v>195</v>
       </c>
       <c r="E107" t="s">
-        <v>6</v>
-      </c>
-      <c r="F107" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B108">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C108">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D108" t="s">
+        <v>194</v>
+      </c>
+      <c r="E108" t="s">
+        <v>4</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>663</v>
+      </c>
+      <c r="B109">
+        <v>108</v>
+      </c>
+      <c r="C109">
+        <v>59</v>
+      </c>
+      <c r="D109" t="s">
         <v>195</v>
       </c>
-      <c r="E108" t="s">
-        <v>5</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>659</v>
-      </c>
-      <c r="B109">
-        <v>107</v>
-      </c>
-      <c r="C109">
-        <v>58</v>
-      </c>
-      <c r="D109" t="s">
-        <v>194</v>
-      </c>
       <c r="E109" t="s">
-        <v>4</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="F109" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B110">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C110">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D110" t="s">
         <v>195</v>
       </c>
       <c r="E110" t="s">
-        <v>3</v>
+        <v>669</v>
       </c>
       <c r="F110" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B111">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C111">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D111" t="s">
         <v>195</v>
       </c>
       <c r="E111" t="s">
-        <v>669</v>
+        <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B112">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C112">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D112" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E112" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" t="s">
-        <v>671</v>
+        <v>674</v>
+      </c>
+      <c r="G112" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="B113">
-        <v>111</v>
-      </c>
-      <c r="C113">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="D113" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E113" t="s">
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="F113" t="s">
-        <v>674</v>
-      </c>
-      <c r="G113" t="s">
-        <v>768</v>
+        <v>679</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="B114">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D114" t="s">
         <v>194</v>
       </c>
       <c r="E114" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="F114" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B115">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D115" t="s">
         <v>194</v>
       </c>
       <c r="E115" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="F115" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B116">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D116" t="s">
         <v>194</v>
       </c>
       <c r="E116" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="F116" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B117">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D117" t="s">
         <v>194</v>
       </c>
       <c r="E117" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="F117" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B118">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D118" t="s">
         <v>194</v>
       </c>
       <c r="E118" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="F118" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B119">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D119" t="s">
         <v>194</v>
       </c>
       <c r="E119" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="F119" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B120">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D120" t="s">
         <v>194</v>
       </c>
       <c r="E120" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="F120" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>709</v>
+        <v>777</v>
       </c>
       <c r="B121">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="C121">
+        <v>63</v>
       </c>
       <c r="D121" t="s">
         <v>194</v>
       </c>
       <c r="E121" t="s">
-        <v>712</v>
+        <v>776</v>
       </c>
       <c r="F121" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>777</v>
-      </c>
-      <c r="B122">
-        <v>120</v>
-      </c>
-      <c r="C122">
-        <v>63</v>
-      </c>
-      <c r="D122" t="s">
-        <v>194</v>
-      </c>
-      <c r="E122" t="s">
         <v>776</v>
       </c>
-      <c r="F122" t="s">
-        <v>776</v>
-      </c>
-      <c r="G122" t="s">
+      <c r="G121" t="s">
         <v>769</v>
       </c>
     </row>
